--- a/static/tickets/Ticket_T-20250709-6.xlsx
+++ b/static/tickets/Ticket_T-20250709-6.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>En Proceso</t>
+          <t>Resuelto</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
